--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487041_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487041_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1267</v>
+        <v>2.3807</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0785</v>
+        <v>3.8143</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9518</v>
+        <v>-1.4336</v>
       </c>
       <c r="G2" t="n">
         <v>3.271</v>
@@ -610,13 +610,13 @@
         <v>1.158</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4853</v>
+        <v>0.7393</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0306</v>
+        <v>0.7664</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4547</v>
+        <v>-0.0271</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8576</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1032</v>
+        <v>1.5761</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0031</v>
+        <v>0.4163</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1063</v>
+        <v>1.1598</v>
       </c>
       <c r="G3" t="n">
         <v>0.8004</v>
@@ -688,13 +688,13 @@
         <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.3824</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4164</v>
+        <v>0.003</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4389</v>
+        <v>-0.3854</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2974</v>
+        <v>0.4094</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3871</v>
+        <v>4.3653</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.0897</v>
+        <v>-3.9559</v>
       </c>
       <c r="G4" t="n">
         <v>1.4869</v>
@@ -766,13 +766,13 @@
         <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8917</v>
+        <v>-0.7796</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1956</v>
+        <v>-0.2174</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.696</v>
+        <v>-0.5622</v>
       </c>
       <c r="V4" t="n">
         <v>-1.842</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1494</v>
+        <v>0.3029</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4599</v>
+        <v>-0.0902</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.393</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6133</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3733</v>
+        <v>-1.5711</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7601</v>
+        <v>2.4305</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.2541</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.9459</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6919</v>
+        <v>1.2288</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6408</v>
+        <v>0.1533</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4274</v>
+        <v>-1.0484</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0682</v>
+        <v>1.2017</v>
       </c>
       <c r="P5" t="n">
-        <v>0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3511</v>
+        <v>1.9301</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3345</v>
+        <v>-0.2707</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8593</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5248</v>
+        <v>-0.1765</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0422</v>
+        <v>-0.2859</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8999</v>
+        <v>1.228</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8576</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.014</v>
+        <v>0.0128</v>
       </c>
       <c r="E6" t="n">
         <v>0.2541</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.268</v>
+        <v>-0.2413</v>
       </c>
       <c r="G6" t="n">
         <v>0.6417</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0416</v>
+        <v>-0.0149</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V6" t="n">
         <v>-0.614</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2038</v>
+        <v>-0.0835</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6503</v>
+        <v>1.4011</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4466</v>
+        <v>-1.4846</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.5668</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5711</v>
+        <v>-0.4636</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4305</v>
+        <v>1.0303</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7060999999999999</v>
+        <v>3.3901</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5227000000000001</v>
+        <v>1.5265</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2288</v>
+        <v>1.8636</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1533</v>
+        <v>-2.8234</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0484</v>
+        <v>-1.9901</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2017</v>
+        <v>-0.8333</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7773</v>
+        <v>-0.5271</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6544</v>
+        <v>-0.3219</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.123</v>
+        <v>-0.2053</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="W7" t="n">
         <v>1.228</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.83</v>
+        <v>-0.1371</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6813</v>
+        <v>-0.9606</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5113</v>
+        <v>0.8235</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5668</v>
+        <v>-0.6133</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4636</v>
+        <v>-2.3733</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0303</v>
+        <v>1.7601</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3901</v>
+        <v>-1.2541</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5265</v>
+        <v>-1.9459</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8636</v>
+        <v>0.6919</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8234</v>
+        <v>0.6408</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9901</v>
+        <v>-0.4274</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8333</v>
+        <v>1.0682</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2737</v>
+        <v>0.0479</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0417</v>
+        <v>0.3586</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.232</v>
+        <v>-0.3107</v>
       </c>
       <c r="V8" t="n">
-        <v>1.228</v>
+        <v>0.0422</v>
       </c>
       <c r="W8" t="n">
-        <v>1.228</v>
+        <v>0.8999</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4745</v>
+        <v>-1.188</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3821</v>
+        <v>-2.1223</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9076</v>
+        <v>0.9343</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1529</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6498</v>
+        <v>-0.3632</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1639</v>
+        <v>0.0959</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4858</v>
+        <v>-0.4591</v>
       </c>
       <c r="V9" t="n">
         <v>0.3281</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8707</v>
+        <v>-1.9778</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6878</v>
+        <v>0.4468</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5585</v>
+        <v>-2.4246</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5794</v>
@@ -1234,13 +1234,13 @@
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0139</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1057</v>
+        <v>-0.3467</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1196</v>
+        <v>0.2535</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8842</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4552</v>
+        <v>-2.1835</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3136</v>
+        <v>-2.9348</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.7513</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4229</v>
@@ -1312,13 +1312,13 @@
         <v>2.7021</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7694</v>
+        <v>-0.4977</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.1289</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2618</v>
+        <v>-0.3689</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9141</v>
+        <v>-2.6405</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.381</v>
+        <v>-2.0805</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5332</v>
+        <v>-0.5599</v>
       </c>
       <c r="G12" t="n">
         <v>0.0297</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7158</v>
+        <v>-0.4422</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5208</v>
+        <v>-0.2204</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.195</v>
+        <v>-0.2218</v>
       </c>
       <c r="V12" t="n">
         <v>-1.842</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.4506</v>
+        <v>-6.818</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7102</v>
+        <v>-5.1311</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7404</v>
+        <v>-1.6869</v>
       </c>
       <c r="G13" t="n">
         <v>-4.8931</v>
@@ -1468,13 +1468,13 @@
         <v>0.965</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2413</v>
+        <v>-0.6088</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8037</v>
+        <v>-0.2247</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4376</v>
+        <v>-0.3841</v>
       </c>
       <c r="V13" t="n">
         <v>0.614</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.5362</v>
+        <v>-10.3465</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.811399999999999</v>
+        <v>-2.621599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.724600000000001</v>
+        <v>-7.7249</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.005699999999999</v>
+        <v>-3.0057</v>
       </c>
       <c r="H14" t="n">
         <v>-5.0406</v>
@@ -1534,10 +1534,10 @@
         <v>-10.0174</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1606999999999998</v>
+        <v>-0.1607000000000003</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9649999999999994</v>
+        <v>0.9650000000000003</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.4755</v>
@@ -1546,13 +1546,13 @@
         <v>15.4406</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.3822</v>
+        <v>-3.1926</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5794</v>
+        <v>-0.3898000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.8028</v>
+        <v>-2.803</v>
       </c>
       <c r="V14" t="n">
         <v>-5.1134</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>13.5832</v>
+        <v>14.0559</v>
       </c>
       <c r="E15" t="n">
-        <v>12.8307</v>
+        <v>13.7319</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7526</v>
+        <v>0.3239</v>
       </c>
       <c r="G15" t="n">
         <v>9.8124</v>
@@ -1624,13 +1624,13 @@
         <v>2.7021</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3258</v>
+        <v>0.7985</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6993</v>
+        <v>0.202</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0251</v>
+        <v>0.5965</v>
       </c>
       <c r="V15" t="n">
         <v>5.5681</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERRANDEZ FERNANDEZ</t>
+          <t>P. SOUZA FIGUEIREDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6008</v>
+        <v>2.2602</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3669</v>
+        <v>1.0752</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2339</v>
+        <v>1.185</v>
       </c>
       <c r="G16" t="n">
-        <v>1.024</v>
+        <v>-1.646</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4492</v>
+        <v>0.7017</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5748</v>
+        <v>-2.3477</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1028</v>
+        <v>-1.166</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0621</v>
+        <v>0.7554</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0407</v>
+        <v>-1.9214</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9212</v>
+        <v>-0.48</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3871</v>
+        <v>-0.0537</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5341</v>
+        <v>-0.4263</v>
       </c>
       <c r="P16" t="n">
         <v>0.579</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7119</v>
+        <v>0.6276</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.5067</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2664</v>
+        <v>0.1209</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2859</v>
+        <v>2.6996</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2859</v>
+        <v>2.6996</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>J. FERRANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.482</v>
+        <v>2.1672</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2832</v>
+        <v>0.666</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1989</v>
+        <v>1.5012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6104000000000001</v>
+        <v>1.024</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3216</v>
+        <v>0.4492</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7112000000000001</v>
+        <v>0.5748</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7778</v>
+        <v>0.1028</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6557</v>
+        <v>0.0621</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1221</v>
+        <v>0.0407</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1674</v>
+        <v>0.9212</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3341</v>
+        <v>0.3871</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8333</v>
+        <v>0.5341</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.193</v>
+        <v>0.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7371</v>
+        <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3928</v>
+        <v>0.2783</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1496</v>
+        <v>0.2773</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2432</v>
+        <v>0.001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3281</v>
+        <v>0.2859</v>
       </c>
       <c r="W17" t="n">
         <v>0.2859</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SOUZA FIGUEIREDO</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8798</v>
+        <v>1.6429</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7748</v>
+        <v>0.0829</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1051</v>
+        <v>1.56</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.646</v>
+        <v>-0.3715</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7017</v>
+        <v>0.7338</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.3477</v>
+        <v>-1.1053</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.166</v>
+        <v>0.4892</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7554</v>
+        <v>1.7023</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9214</v>
+        <v>-1.2131</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.48</v>
+        <v>-0.8607</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0537</v>
+        <v>-0.9685</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4263</v>
+        <v>0.1078</v>
       </c>
       <c r="P18" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2472</v>
+        <v>0.8057</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2062</v>
+        <v>0.3573</v>
       </c>
       <c r="U18" t="n">
-        <v>0.041</v>
+        <v>0.4484</v>
       </c>
       <c r="V18" t="n">
-        <v>2.6996</v>
+        <v>0.2436</v>
       </c>
       <c r="W18" t="n">
-        <v>2.6996</v>
+        <v>0.2014</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6363</v>
+        <v>1.3068</v>
       </c>
       <c r="E19" t="n">
-        <v>0.183</v>
+        <v>1.0815</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4533</v>
+        <v>0.2253</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3715</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7338</v>
+        <v>1.3216</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1053</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4892</v>
+        <v>1.7778</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7023</v>
+        <v>1.6557</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2131</v>
+        <v>0.1221</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8607</v>
+        <v>-1.1674</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9685</v>
+        <v>-0.3341</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1078</v>
+        <v>-0.8333</v>
       </c>
       <c r="P19" t="n">
-        <v>0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7991</v>
+        <v>1.2175</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4574</v>
+        <v>0.9479</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3417</v>
+        <v>0.2697</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2436</v>
+        <v>-0.3281</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2014</v>
+        <v>0.2859</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0422</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8927</v>
+        <v>-0.1177</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0866</v>
+        <v>1.4872</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9794</v>
+        <v>-1.6049</v>
       </c>
       <c r="G20" t="n">
         <v>0.6201</v>
@@ -2014,13 +2014,13 @@
         <v>0.579</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8639</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7139</v>
+        <v>-0.3133</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1501</v>
+        <v>0.2244</v>
       </c>
       <c r="V20" t="n">
         <v>-1.228</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9272</v>
+        <v>-1.7067</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8673</v>
+        <v>-1.9675</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0598</v>
+        <v>0.2608</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8335</v>
@@ -2092,13 +2092,13 @@
         <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5552</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3834</v>
+        <v>0.2833</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1718</v>
+        <v>0.4924</v>
       </c>
       <c r="V21" t="n">
         <v>-1.842</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7551</v>
+        <v>-2.0399</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1882</v>
+        <v>-3.0881</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4332</v>
+        <v>1.0482</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7898</v>
@@ -2170,13 +2170,13 @@
         <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3206</v>
+        <v>1.0358</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3239</v>
+        <v>0.4241</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0033</v>
+        <v>0.6117</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2859</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0711</v>
+        <v>-4.6973</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7449</v>
+        <v>-5.3444</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6738</v>
+        <v>0.6471</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4206</v>
@@ -2248,13 +2248,13 @@
         <v>1.3511</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1064</v>
+        <v>0.2674</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2829</v>
+        <v>0.1177</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1765</v>
+        <v>0.1497</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.536</v>
+        <v>12.8714</v>
       </c>
       <c r="E24" t="n">
-        <v>7.724800000000001</v>
+        <v>7.7247</v>
       </c>
       <c r="F24" t="n">
-        <v>3.811599999999999</v>
+        <v>5.1466</v>
       </c>
       <c r="G24" t="n">
-        <v>3.005500000000001</v>
+        <v>3.0055</v>
       </c>
       <c r="H24" t="n">
         <v>5.0406</v>
@@ -2305,7 +2305,7 @@
         <v>10.0174</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1608000000000009</v>
+        <v>0.1608000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-7.1727</v>
@@ -2326,16 +2326,16 @@
         <v>14.4757</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3823</v>
+        <v>5.717600000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8027</v>
+        <v>2.803</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5795</v>
+        <v>2.9147</v>
       </c>
       <c r="V24" t="n">
-        <v>5.113200000000001</v>
+        <v>5.113200000000002</v>
       </c>
       <c r="W24" t="n">
         <v>10.1844</v>
